--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-02-2026.xlsx
@@ -2204,7 +2204,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationsuperstore.co.uk', port=443): Max retries exceeded with url: /product/celotex-52-5mm-insulated-plasterboard-pl4040.html (Caused by NewConnectionError('&lt;urllib3.connection.HTTPSConnection object at 0x000001C3EFE47210&gt;: Failed to establish a new connection: [Errno 11001] getaddrinfo failed'))</t>
+          <t>£46.50</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
